--- a/public/管理口径原因分析默认模版/上海物业项目部.xlsx
+++ b/public/管理口径原因分析默认模版/上海物业项目部.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255" firstSheet="9" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="目录" state="visible" r:id="rId4"/>
@@ -12,23 +12,24 @@
     <sheet sheetId="4" name="上海同盛大厦项目" state="visible" r:id="rId6"/>
     <sheet sheetId="5" name="豪孚迪安保项目" state="visible" r:id="rId7"/>
     <sheet sheetId="6" name="华东化工仓储安保项目" state="visible" r:id="rId8"/>
-    <sheet sheetId="7" name="寰球工程安保项目" state="visible" r:id="rId9"/>
-    <sheet sheetId="8" name="寰球工程保洁项目" state="visible" r:id="rId10"/>
-    <sheet sheetId="9" name="长泰影院保洁项目" state="visible" r:id="rId11"/>
-    <sheet sheetId="10" name="川沙影院保洁项目" state="visible" r:id="rId12"/>
-    <sheet sheetId="11" name="上海世纪大道中石油综合物业项目" state="visible" r:id="rId13"/>
-    <sheet sheetId="12" name="上海世纪大道中石油综合餐饮项目" state="visible" r:id="rId14"/>
-    <sheet sheetId="13" name="世纪大道中石油上海大厦能源转售项目" state="visible" r:id="rId15"/>
-    <sheet sheetId="14" name="中石油上海临港新材料研究院配餐项目" state="visible" r:id="rId16"/>
-    <sheet sheetId="15" name="中石油上海临港新材料研究院物业项目" state="visible" r:id="rId17"/>
-    <sheet sheetId="16" name="陆家嘴金融城白领文化艺术中心物业项目" state="visible" r:id="rId18"/>
+    <sheet sheetId="7" name="寰球工程物业项目_合并" state="visible" r:id="rId9"/>
+    <sheet sheetId="8" name="寰球工程物业项目_222200150224" state="visible" r:id="rId10"/>
+    <sheet sheetId="9" name="寰球工程物业项目_222200150225" state="visible" r:id="rId11"/>
+    <sheet sheetId="10" name="长泰影院保洁项目" state="visible" r:id="rId12"/>
+    <sheet sheetId="11" name="川沙影院保洁项目" state="visible" r:id="rId13"/>
+    <sheet sheetId="12" name="上海世纪大道中石油综合物业项目" state="visible" r:id="rId14"/>
+    <sheet sheetId="13" name="上海世纪大道中石油综合餐饮项目" state="visible" r:id="rId15"/>
+    <sheet sheetId="14" name="世纪大道中石油上海大厦能源转售项目" state="visible" r:id="rId16"/>
+    <sheet sheetId="15" name="中石油上海临港新材料研究院配餐项目" state="visible" r:id="rId17"/>
+    <sheet sheetId="16" name="中石油上海临港新材料研究院物业项目" state="visible" r:id="rId18"/>
+    <sheet sheetId="17" name="陆家嘴金融城白领文化艺术中心物业项目" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="120">
   <si>
     <t>工作表目录</t>
   </si>
@@ -54,10 +55,13 @@
     <t>华东化工仓储安保项目</t>
   </si>
   <si>
-    <t>寰球工程安保项目</t>
+    <t>寰球工程物业项目_合并</t>
   </si>
   <si>
-    <t>寰球工程保洁项目</t>
+    <t>寰球工程物业项目_222200150224</t>
+  </si>
+  <si>
+    <t>寰球工程物业项目_222200150225</t>
   </si>
   <si>
     <t>长泰影院保洁项目</t>
@@ -84,7 +88,7 @@
     <t>陆家嘴金融城白领文化艺术中心物业项目</t>
   </si>
   <si>
-    <t>合计预算执行分析（2026年07月）</t>
+    <t>合计预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>项目</t>
@@ -133,10 +137,10 @@
     <t>一、 营业收入</t>
   </si>
   <si>
-    <t>1、新增代售酒水收入167万元；2、增加礼仪人工收入259万元；3、临港增加547万元；4、餐饮增加125万元；5、同盛减少49万元</t>
+    <t>1、新增代售酒水收入167万元；2、增加礼仪人工收入302万元；3、临港增加480万元；4、餐饮增加125万元；5、同盛减少69万元</t>
   </si>
   <si>
-    <t>1、新增代售酒水收入167万元；2、增加礼仪人工收入91万元；3、临港减少23万元；4、餐饮增加60万元；5、同盛减少38万元</t>
+    <t>1、上海大厦物业增加234万元；2、临港减少35万元；3、餐饮增加62万元；4、同盛减少51万元</t>
   </si>
   <si>
     <t xml:space="preserve">     减:（一）经营性采购支出</t>
@@ -145,7 +149,7 @@
     <t>1、新增代售酒水成本167万元；2、餐饮多入帐上年成本70万元</t>
   </si>
   <si>
-    <t>1、新增代售酒水成本167万元；2、餐饮减少10万元、临港减少11万元</t>
+    <t>1、新增代售酒水成本167万元；2、餐饮减少14万元、临港减少12万元</t>
   </si>
   <si>
     <t xml:space="preserve">         其中：1.外购材料</t>
@@ -187,7 +191,7 @@
     <t xml:space="preserve">        （五）用工薪酬成本</t>
   </si>
   <si>
-    <t>1、临港增加380万元；2、上海大厦减少107万元</t>
+    <t>1、临港增加396万元；2、上海大厦减少72万元</t>
   </si>
   <si>
     <t>主要是上海大厦项目</t>
@@ -196,7 +200,7 @@
     <t xml:space="preserve">        （六）外包劳务支出</t>
   </si>
   <si>
-    <t>礼仪人工成本增加198万元</t>
+    <t>礼仪人工成本增加221万元</t>
   </si>
   <si>
     <t>主要是礼仪人工的增加</t>
@@ -285,7 +289,7 @@
     <t>四、净利润</t>
   </si>
   <si>
-    <t>上海同盛大厦项目预算执行分析（2026年07月）</t>
+    <t>上海同盛大厦项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>出租率、平均单价同比均下降</t>
@@ -303,40 +307,40 @@
     <t>因出租率下降，中介费减少</t>
   </si>
   <si>
-    <t>豪孚迪安保项目预算执行分析（2026年07月）</t>
+    <t>豪孚迪安保项目预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>华东化工仓储安保项目预算执行分析（2026年07月）</t>
+    <t>华东化工仓储安保项目预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>寰球工程安保项目预算执行分析（2026年07月）</t>
+    <t>寰球工程物业项目_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>上年同期部分收入未进账</t>
+    <t>上年同期部分外包支出未入账</t>
   </si>
   <si>
-    <t>上年同期部分成本费用未进账</t>
+    <t>寰球工程物业项目_222200150224预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>寰球工程保洁项目预算执行分析（2026年07月）</t>
+    <t>寰球工程物业项目_222200150225预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>长泰影院保洁项目预算执行分析（2026年07月）</t>
+    <t>长泰影院保洁项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>此项目今年终止</t>
   </si>
   <si>
-    <t>川沙影院保洁项目预算执行分析（2026年07月）</t>
+    <t>川沙影院保洁项目预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>上海世纪大道中石油综合物业项目预算执行分析（2026年07月）</t>
+    <t>上海世纪大道中石油综合物业项目预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>1、新增代售酒水收入167万元；2、增加礼仪人工收入259万元</t>
+    <t>1、新增代售酒水收入167万元；2、增加礼仪人工收入302万元</t>
   </si>
   <si>
-    <t>1、新增代售酒水收入167万元；2、增加礼仪人工收入91万元</t>
+    <t>1、新增代售酒水收入167万元；2、增加礼仪人工收入122万元；3、工程维修收入减少70万元</t>
   </si>
   <si>
     <t>新增代售酒水成本167万元</t>
@@ -351,7 +355,7 @@
     <t>与预算周期不同</t>
   </si>
   <si>
-    <t>上海世纪大道中石油综合餐饮项目预算执行分析（2026年07月）</t>
+    <t>上海世纪大道中石油综合餐饮项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>今年入账了上年80万收入，且上年同期约50万元当期收入未进账</t>
@@ -369,22 +373,22 @@
     <t>今年同比减少了超市租金</t>
   </si>
   <si>
-    <t>1、今年食材成本率同比下降39.3%；2、商品销售收入增加132万元；3、减少租金费用16万元；4、压降用工成本等经营费用</t>
+    <t>1、今年食材成本率同比下降约36%；2、商品销售收入增加138万元；3、减少租金费用18万元；4、压降用工成本等经营费用</t>
   </si>
   <si>
-    <t>1、今年食材成本率相比预算下降29.8%；2、商品销售收入增加78万元；3、压降用工成本等经营费用</t>
+    <t>1、今年食材成本率相比预算下降约29%；2、商品销售收入增加86万元；3、压降用工成本等经营费用</t>
   </si>
   <si>
-    <t>世纪大道中石油上海大厦能源转售项目预算执行分析（2026年07月）</t>
+    <t>世纪大道中石油上海大厦能源转售项目预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>中石油上海临港新材料研究院配餐项目预算执行分析（2026年07月）</t>
+    <t>中石油上海临港新材料研究院配餐项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>该项目为上年新增项目</t>
   </si>
   <si>
-    <t>中石油上海临港新材料研究院物业项目预算执行分析（2026年07月）</t>
+    <t>中石油上海临港新材料研究院物业项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>甲方今年严格控制成本费用发生</t>
@@ -399,7 +403,10 @@
     <t>上年同期对应收入未完全进账</t>
   </si>
   <si>
-    <t>陆家嘴金融城白领文化艺术中心物业项目预算执行分析（2026年07月）</t>
+    <t>陆家嘴金融城白领文化艺术中心物业项目预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>上年同期部分收入未进账</t>
   </si>
   <si>
     <t>上年同期成本费用未进账</t>
@@ -907,7 +914,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -925,51 +932,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -977,7 +984,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
@@ -989,7 +996,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1007,7 +1014,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -1025,7 +1032,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -1043,7 +1050,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -1061,7 +1068,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -1079,7 +1086,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -1097,7 +1104,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -1115,7 +1122,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -1133,7 +1140,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -1151,7 +1158,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -1169,7 +1176,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -1187,7 +1194,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -1205,7 +1212,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -1223,7 +1230,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -1241,7 +1248,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -1259,7 +1266,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -1277,7 +1284,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -1295,7 +1302,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -1313,7 +1320,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -1331,7 +1338,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -1349,7 +1356,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -1367,7 +1374,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -1385,7 +1392,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -1403,7 +1410,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -1421,7 +1428,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -1439,7 +1446,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -1457,7 +1464,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -1475,7 +1482,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -1493,7 +1500,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -1511,7 +1518,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -1529,7 +1536,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -1547,7 +1554,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -1565,7 +1572,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -1583,7 +1590,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -1601,7 +1608,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -1619,7 +1626,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -1637,7 +1644,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -1692,51 +1699,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -1744,12 +1751,10 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H3" s="11"/>
-      <c r="I3" s="12" t="s">
-        <v>95</v>
-      </c>
+      <c r="I3" s="12"/>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -1758,7 +1763,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1776,7 +1781,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -1794,7 +1799,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -1812,7 +1817,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -1830,7 +1835,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -1846,22 +1851,18 @@
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="12" t="s">
-        <v>96</v>
-      </c>
+      <c r="G9" s="12"/>
       <c r="H9" s="11"/>
-      <c r="I9" s="12" t="s">
-        <v>96</v>
-      </c>
+      <c r="I9" s="12"/>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
@@ -1870,7 +1871,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -1888,7 +1889,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -1906,7 +1907,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -1924,7 +1925,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -1942,7 +1943,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -1960,7 +1961,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -1978,7 +1979,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -1994,44 +1995,36 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12" t="s">
-        <v>97</v>
-      </c>
+      <c r="G17" s="12"/>
       <c r="H17" s="11"/>
-      <c r="I17" s="12" t="s">
-        <v>97</v>
-      </c>
+      <c r="I17" s="12"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
     </row>
-    <row r="18" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12" t="s">
-        <v>54</v>
-      </c>
+      <c r="G18" s="12"/>
       <c r="H18" s="11"/>
-      <c r="I18" s="12" t="s">
-        <v>98</v>
-      </c>
+      <c r="I18" s="12"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
@@ -2040,7 +2033,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -2049,9 +2042,7 @@
       <c r="F19" s="11"/>
       <c r="G19" s="12"/>
       <c r="H19" s="11"/>
-      <c r="I19" s="12" t="s">
-        <v>99</v>
-      </c>
+      <c r="I19" s="12"/>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
@@ -2060,7 +2051,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -2069,9 +2060,7 @@
       <c r="F20" s="11"/>
       <c r="G20" s="12"/>
       <c r="H20" s="11"/>
-      <c r="I20" s="12" t="s">
-        <v>99</v>
-      </c>
+      <c r="I20" s="12"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
@@ -2080,7 +2069,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -2098,7 +2087,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -2107,9 +2096,7 @@
       <c r="F22" s="11"/>
       <c r="G22" s="12"/>
       <c r="H22" s="11"/>
-      <c r="I22" s="12" t="s">
-        <v>99</v>
-      </c>
+      <c r="I22" s="12"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
@@ -2118,7 +2105,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -2136,7 +2123,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -2154,7 +2141,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -2172,7 +2159,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -2181,9 +2168,7 @@
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
       <c r="H26" s="11"/>
-      <c r="I26" s="12" t="s">
-        <v>99</v>
-      </c>
+      <c r="I26" s="12"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -2192,7 +2177,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -2210,7 +2195,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -2228,7 +2213,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -2246,7 +2231,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -2264,7 +2249,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -2282,7 +2267,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -2300,7 +2285,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -2318,7 +2303,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -2336,7 +2321,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -2354,7 +2339,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -2372,7 +2357,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -2390,7 +2375,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -2408,7 +2393,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -2426,7 +2411,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -2463,7 +2448,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2481,51 +2466,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -2533,11 +2518,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -2547,7 +2532,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -2565,7 +2550,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -2581,18 +2566,16 @@
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="12" t="s">
-        <v>103</v>
-      </c>
+      <c r="G6" s="12"/>
       <c r="H6" s="11"/>
       <c r="I6" s="12"/>
       <c r="J6" s="11"/>
@@ -2603,7 +2586,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -2621,7 +2604,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -2637,18 +2620,22 @@
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
+      <c r="G9" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
+      <c r="I9" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
@@ -2657,7 +2644,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -2675,7 +2662,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -2693,7 +2680,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -2711,7 +2698,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -2729,7 +2716,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -2747,7 +2734,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -2765,7 +2752,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -2781,9 +2768,9 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -2791,28 +2778,34 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
+      <c r="I17" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
+      <c r="G18" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
+      <c r="I18" s="12" t="s">
+        <v>99</v>
+      </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
@@ -2821,7 +2814,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -2839,7 +2832,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -2848,7 +2841,9 @@
       <c r="F20" s="11"/>
       <c r="G20" s="12"/>
       <c r="H20" s="11"/>
-      <c r="I20" s="12"/>
+      <c r="I20" s="12" t="s">
+        <v>100</v>
+      </c>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
@@ -2857,7 +2852,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -2875,7 +2870,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -2884,7 +2879,9 @@
       <c r="F22" s="11"/>
       <c r="G22" s="12"/>
       <c r="H22" s="11"/>
-      <c r="I22" s="12"/>
+      <c r="I22" s="12" t="s">
+        <v>100</v>
+      </c>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
@@ -2893,7 +2890,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -2911,7 +2908,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -2927,18 +2924,16 @@
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
     </row>
-    <row r="25" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="12" t="s">
-        <v>105</v>
-      </c>
+      <c r="G25" s="12"/>
       <c r="H25" s="11"/>
       <c r="I25" s="12"/>
       <c r="J25" s="11"/>
@@ -2949,7 +2944,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -2958,7 +2953,9 @@
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
       <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
+      <c r="I26" s="12" t="s">
+        <v>100</v>
+      </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -2967,7 +2964,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -2985,7 +2982,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -3003,7 +3000,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -3021,7 +3018,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -3039,7 +3036,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -3057,7 +3054,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -3075,7 +3072,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -3093,7 +3090,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -3111,7 +3108,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -3129,7 +3126,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -3147,7 +3144,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -3163,22 +3160,18 @@
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
     </row>
-    <row r="38" ht="112.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="12" t="s">
-        <v>106</v>
-      </c>
+      <c r="G38" s="12"/>
       <c r="H38" s="11"/>
-      <c r="I38" s="12" t="s">
-        <v>107</v>
-      </c>
+      <c r="I38" s="12"/>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
@@ -3187,7 +3180,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -3205,7 +3198,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -3242,7 +3235,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -3260,60 +3253,64 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
+      <c r="G3" s="12" t="s">
+        <v>102</v>
+      </c>
       <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
+      <c r="I3" s="12" t="s">
+        <v>103</v>
+      </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -3322,7 +3319,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -3340,7 +3337,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -3356,16 +3353,18 @@
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
+      <c r="G6" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12"/>
       <c r="J6" s="11"/>
@@ -3376,7 +3375,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -3394,7 +3393,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -3412,7 +3411,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -3430,7 +3429,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -3448,7 +3447,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -3466,7 +3465,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -3484,7 +3483,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -3502,7 +3501,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -3520,7 +3519,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -3538,7 +3537,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -3556,14 +3555,16 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
+      <c r="G17" s="12" t="s">
+        <v>105</v>
+      </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
       <c r="J17" s="11"/>
@@ -3574,7 +3575,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -3592,7 +3593,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -3610,7 +3611,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -3628,7 +3629,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -3646,7 +3647,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -3664,7 +3665,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -3682,7 +3683,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -3698,16 +3699,18 @@
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="12"/>
+      <c r="G25" s="12" t="s">
+        <v>106</v>
+      </c>
       <c r="H25" s="11"/>
       <c r="I25" s="12"/>
       <c r="J25" s="11"/>
@@ -3718,7 +3721,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -3736,7 +3739,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -3754,7 +3757,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -3772,7 +3775,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -3790,7 +3793,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -3808,7 +3811,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -3826,7 +3829,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -3844,7 +3847,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -3862,7 +3865,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -3880,7 +3883,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -3898,7 +3901,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -3916,7 +3919,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -3932,18 +3935,22 @@
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" ht="112.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
+      <c r="G38" s="12" t="s">
+        <v>107</v>
+      </c>
       <c r="H38" s="11"/>
-      <c r="I38" s="12"/>
+      <c r="I38" s="12" t="s">
+        <v>108</v>
+      </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
@@ -3952,7 +3959,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -3970,7 +3977,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -4025,60 +4032,58 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12" t="s">
-        <v>110</v>
-      </c>
+      <c r="G3" s="12"/>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
       <c r="J3" s="11"/>
@@ -4089,7 +4094,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -4107,7 +4112,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -4125,7 +4130,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -4143,7 +4148,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -4161,7 +4166,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -4179,7 +4184,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -4197,7 +4202,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -4215,7 +4220,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -4233,7 +4238,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -4251,7 +4256,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -4269,7 +4274,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -4287,7 +4292,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -4305,7 +4310,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -4323,7 +4328,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -4341,7 +4346,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -4359,7 +4364,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -4377,7 +4382,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4395,7 +4400,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -4413,7 +4418,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -4431,7 +4436,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -4449,7 +4454,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -4467,7 +4472,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -4485,7 +4490,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -4503,7 +4508,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -4521,7 +4526,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -4539,7 +4544,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -4557,7 +4562,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -4575,7 +4580,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -4593,7 +4598,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -4611,7 +4616,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -4629,7 +4634,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -4647,7 +4652,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -4665,7 +4670,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -4683,7 +4688,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -4701,7 +4706,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -4719,7 +4724,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -4737,7 +4742,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -4774,7 +4779,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4792,51 +4797,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -4844,7 +4849,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
@@ -4856,7 +4861,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -4874,7 +4879,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -4892,7 +4897,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -4908,9 +4913,9 @@
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
     </row>
-    <row r="7" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -4919,9 +4924,7 @@
       <c r="F7" s="11"/>
       <c r="G7" s="12"/>
       <c r="H7" s="11"/>
-      <c r="I7" s="12" t="s">
-        <v>112</v>
-      </c>
+      <c r="I7" s="12"/>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
@@ -4930,7 +4933,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -4948,7 +4951,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -4966,7 +4969,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -4984,7 +4987,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -5002,7 +5005,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -5020,7 +5023,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -5038,7 +5041,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -5056,7 +5059,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -5074,7 +5077,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -5090,9 +5093,9 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -5101,9 +5104,7 @@
       <c r="F17" s="11"/>
       <c r="G17" s="12"/>
       <c r="H17" s="11"/>
-      <c r="I17" s="12" t="s">
-        <v>113</v>
-      </c>
+      <c r="I17" s="12"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
@@ -5112,7 +5113,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -5130,7 +5131,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -5148,7 +5149,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -5166,7 +5167,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -5184,7 +5185,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -5193,9 +5194,7 @@
       <c r="F22" s="11"/>
       <c r="G22" s="12"/>
       <c r="H22" s="11"/>
-      <c r="I22" s="12" t="s">
-        <v>114</v>
-      </c>
+      <c r="I22" s="12"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
@@ -5204,7 +5203,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -5222,7 +5221,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -5240,7 +5239,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -5258,7 +5257,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -5276,7 +5275,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -5294,7 +5293,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -5312,7 +5311,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -5330,7 +5329,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -5348,7 +5347,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -5366,7 +5365,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -5384,7 +5383,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -5402,7 +5401,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -5420,7 +5419,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -5438,7 +5437,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -5456,7 +5455,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -5472,18 +5471,16 @@
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
     </row>
-    <row r="38" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="12" t="s">
-        <v>115</v>
-      </c>
+      <c r="G38" s="12"/>
       <c r="H38" s="11"/>
       <c r="I38" s="12"/>
       <c r="J38" s="11"/>
@@ -5494,7 +5491,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -5512,7 +5509,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -5549,7 +5546,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5567,51 +5564,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -5619,7 +5616,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
@@ -5631,7 +5628,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -5649,7 +5646,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -5667,7 +5664,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -5683,9 +5680,784 @@
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
     </row>
+    <row r="7" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+    </row>
+    <row r="17" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+    </row>
+    <row r="38" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="H38" s="11"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N40"/>
+  <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="53" style="6" customWidth="1"/>
+    <col min="2" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="24.3333333333333" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="24.3333333333333" customWidth="1"/>
+    <col min="10" max="14" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+    </row>
+    <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+    </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -5703,7 +6475,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -5721,7 +6493,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -5739,7 +6511,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -5757,7 +6529,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -5775,7 +6547,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -5793,7 +6565,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -5811,7 +6583,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -5829,7 +6601,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -5847,7 +6619,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -5865,7 +6637,7 @@
     </row>
     <row r="17" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -5873,7 +6645,7 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
@@ -5885,7 +6657,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -5903,7 +6675,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -5921,7 +6693,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -5939,7 +6711,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -5957,7 +6729,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -5975,7 +6747,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -5993,7 +6765,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -6011,7 +6783,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -6029,7 +6801,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -6047,7 +6819,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -6065,7 +6837,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -6083,7 +6855,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -6101,7 +6873,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -6119,7 +6891,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -6137,7 +6909,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -6155,7 +6927,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -6173,7 +6945,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -6191,7 +6963,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -6209,7 +6981,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -6227,7 +6999,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -6245,7 +7017,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -6263,7 +7035,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -6281,7 +7053,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -6305,7 +7077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="0" outlineLevelCol="2" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6377,7 +7149,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="5" t="str">
-        <f>HYPERLINK("#'寰球工程安保项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'寰球工程物业项目_合并'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -6387,7 +7159,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="5" t="str">
-        <f>HYPERLINK("#'寰球工程保洁项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'寰球工程物业项目_222200150224'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -6397,7 +7169,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="5" t="str">
-        <f>HYPERLINK("#'长泰影院保洁项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'寰球工程物业项目_222200150225'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -6407,7 +7179,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="5" t="str">
-        <f>HYPERLINK("#'川沙影院保洁项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'长泰影院保洁项目'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -6417,7 +7189,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="5" t="str">
-        <f>HYPERLINK("#'上海世纪大道中石油综合物业项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'川沙影院保洁项目'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -6427,7 +7199,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="5" t="str">
-        <f>HYPERLINK("#'上海世纪大道中石油综合餐饮项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'上海世纪大道中石油综合物业项目'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -6437,7 +7209,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="5" t="str">
-        <f>HYPERLINK("#'世纪大道中石油上海大厦能源转售项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'上海世纪大道中石油综合餐饮项目'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -6447,7 +7219,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="5" t="str">
-        <f>HYPERLINK("#'中石油上海临港新材料研究院配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'世纪大道中石油上海大厦能源转售项目'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -6457,7 +7229,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="5" t="str">
-        <f>HYPERLINK("#'中石油上海临港新材料研究院物业项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'中石油上海临港新材料研究院配餐项目'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -6467,6 +7239,16 @@
         <v>17</v>
       </c>
       <c r="C16" s="5" t="str">
+        <f>HYPERLINK("#'中石油上海临港新材料研究院物业项目'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="5" t="str">
         <f>HYPERLINK("#'陆家嘴金融城白领文化艺术中心物业项目'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
@@ -6495,7 +7277,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -6513,51 +7295,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="131.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -6565,11 +7347,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -6579,7 +7361,7 @@
     </row>
     <row r="4" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -6587,11 +7369,11 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
@@ -6601,7 +7383,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -6619,7 +7401,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -6637,7 +7419,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -6655,7 +7437,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -6673,7 +7455,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -6691,7 +7473,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -6709,7 +7491,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -6727,7 +7509,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -6745,7 +7527,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -6763,7 +7545,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -6781,7 +7563,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -6799,7 +7581,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -6817,7 +7599,7 @@
     </row>
     <row r="17" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -6825,11 +7607,11 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
@@ -6839,7 +7621,7 @@
     </row>
     <row r="18" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -6847,11 +7629,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -6861,7 +7643,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -6879,7 +7661,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -6897,7 +7679,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -6915,7 +7697,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -6933,7 +7715,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -6951,7 +7733,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -6969,7 +7751,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -6987,7 +7769,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -7005,7 +7787,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -7023,7 +7805,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -7041,7 +7823,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -7059,7 +7841,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -7077,7 +7859,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -7095,7 +7877,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -7113,7 +7895,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -7131,7 +7913,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -7149,7 +7931,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -7167,7 +7949,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -7185,7 +7967,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -7203,7 +7985,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -7221,7 +8003,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -7239,7 +8021,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -7276,7 +8058,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -7294,51 +8076,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -7346,11 +8128,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -7360,7 +8142,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -7378,7 +8160,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -7396,7 +8178,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -7414,7 +8196,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -7432,7 +8214,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -7450,7 +8232,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -7468,7 +8250,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -7486,7 +8268,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -7504,7 +8286,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -7522,7 +8304,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -7540,7 +8322,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -7558,7 +8340,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -7576,7 +8358,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -7594,7 +8376,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -7612,7 +8394,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -7630,7 +8412,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -7648,7 +8430,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -7666,7 +8448,7 @@
     </row>
     <row r="21" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -7674,11 +8456,11 @@
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" s="11"/>
       <c r="I21" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
@@ -7688,7 +8470,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -7706,7 +8488,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -7724,7 +8506,7 @@
     </row>
     <row r="24" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -7732,7 +8514,7 @@
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="12"/>
@@ -7744,7 +8526,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -7762,7 +8544,7 @@
     </row>
     <row r="26" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -7770,7 +8552,7 @@
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="12"/>
@@ -7782,7 +8564,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -7800,7 +8582,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -7818,7 +8600,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -7836,7 +8618,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -7854,7 +8636,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -7872,7 +8654,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -7890,7 +8672,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -7908,7 +8690,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -7926,7 +8708,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -7944,7 +8726,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -7962,7 +8744,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -7980,7 +8762,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -7998,7 +8780,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -8016,7 +8798,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -8053,7 +8835,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -8071,51 +8853,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -8133,7 +8915,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -8151,7 +8933,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -8169,7 +8951,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -8187,7 +8969,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -8205,7 +8987,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -8223,7 +9005,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -8241,7 +9023,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -8259,7 +9041,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -8277,7 +9059,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -8295,7 +9077,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -8313,7 +9095,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -8331,7 +9113,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -8349,7 +9131,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -8367,7 +9149,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -8385,7 +9167,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -8403,7 +9185,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -8421,7 +9203,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -8439,7 +9221,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -8457,7 +9239,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -8475,7 +9257,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -8493,7 +9275,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -8511,7 +9293,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -8529,7 +9311,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -8547,7 +9329,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -8565,7 +9347,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -8583,7 +9365,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -8601,7 +9383,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -8619,7 +9401,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -8637,7 +9419,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -8655,7 +9437,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -8673,7 +9455,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -8691,7 +9473,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -8709,7 +9491,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -8727,7 +9509,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -8745,7 +9527,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -8763,7 +9545,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -8781,7 +9563,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -8818,7 +9600,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -8836,51 +9618,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -8898,7 +9680,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -8916,7 +9698,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -8934,7 +9716,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -8952,7 +9734,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -8970,7 +9752,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -8988,7 +9770,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -9006,7 +9788,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -9024,7 +9806,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -9042,7 +9824,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -9060,7 +9842,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -9078,7 +9860,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -9096,7 +9878,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -9114,7 +9896,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -9132,7 +9914,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -9150,7 +9932,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -9168,7 +9950,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -9186,7 +9968,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -9204,7 +9986,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -9222,7 +10004,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -9240,7 +10022,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -9258,7 +10040,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -9276,7 +10058,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -9294,7 +10076,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -9312,7 +10094,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -9330,7 +10112,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -9348,7 +10130,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -9366,7 +10148,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -9384,7 +10166,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -9402,7 +10184,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -9420,7 +10202,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -9438,7 +10220,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -9456,7 +10238,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -9474,7 +10256,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -9492,7 +10274,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -9510,7 +10292,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -9528,7 +10310,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -9546,7 +10328,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -9583,7 +10365,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -9601,60 +10383,58 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12" t="s">
-        <v>87</v>
-      </c>
+      <c r="G3" s="12"/>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
       <c r="J3" s="11"/>
@@ -9665,7 +10445,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -9683,7 +10463,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -9701,7 +10481,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -9719,7 +10499,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -9737,7 +10517,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -9755,7 +10535,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -9773,7 +10553,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -9791,7 +10571,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -9809,7 +10589,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -9827,7 +10607,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -9845,7 +10625,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -9863,7 +10643,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -9881,7 +10661,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -9897,18 +10677,16 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12" t="s">
-        <v>88</v>
-      </c>
+      <c r="G17" s="12"/>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
       <c r="J17" s="11"/>
@@ -9919,7 +10697,7 @@
     </row>
     <row r="18" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -9939,7 +10717,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -9957,7 +10735,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -9975,7 +10753,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -9993,7 +10771,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -10011,7 +10789,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -10029,7 +10807,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -10047,7 +10825,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -10065,7 +10843,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -10083,7 +10861,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -10101,7 +10879,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -10119,7 +10897,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -10137,7 +10915,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -10155,7 +10933,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -10173,7 +10951,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -10191,7 +10969,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -10209,7 +10987,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -10227,7 +11005,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -10245,7 +11023,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -10263,7 +11041,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -10281,7 +11059,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -10299,7 +11077,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -10317,7 +11095,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -10372,51 +11150,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -10434,7 +11212,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -10452,7 +11230,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -10470,7 +11248,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -10488,7 +11266,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -10506,7 +11284,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -10524,7 +11302,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -10542,7 +11320,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -10560,7 +11338,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -10578,7 +11356,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -10596,7 +11374,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -10614,7 +11392,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -10632,7 +11410,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -10650,7 +11428,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -10668,7 +11446,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -10686,7 +11464,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -10704,7 +11482,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -10722,7 +11500,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -10740,7 +11518,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -10758,7 +11536,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -10776,7 +11554,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -10794,7 +11572,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -10812,7 +11590,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -10830,7 +11608,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -10848,7 +11626,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -10866,7 +11644,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -10884,7 +11662,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -10902,7 +11680,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -10920,7 +11698,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -10938,7 +11716,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -10956,7 +11734,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -10974,7 +11752,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -10992,7 +11770,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -11010,7 +11788,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -11028,7 +11806,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -11046,7 +11824,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -11064,7 +11842,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -11082,7 +11860,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -11137,60 +11915,58 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12" t="s">
-        <v>91</v>
-      </c>
+      <c r="G3" s="12"/>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
       <c r="J3" s="11"/>
@@ -11201,7 +11977,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -11219,7 +11995,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -11237,7 +12013,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -11255,7 +12031,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -11273,7 +12049,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -11291,7 +12067,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -11309,7 +12085,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -11327,7 +12103,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -11345,7 +12121,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -11363,7 +12139,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -11381,7 +12157,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -11399,7 +12175,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -11417,7 +12193,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -11435,7 +12211,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -11453,7 +12229,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -11471,7 +12247,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -11489,7 +12265,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -11507,7 +12283,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -11525,7 +12301,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -11543,7 +12319,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -11561,7 +12337,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -11579,7 +12355,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -11597,7 +12373,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -11615,7 +12391,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -11633,7 +12409,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -11651,7 +12427,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -11669,7 +12445,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -11687,7 +12463,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -11705,7 +12481,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -11723,7 +12499,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -11741,7 +12517,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -11759,7 +12535,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -11777,7 +12553,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -11795,7 +12571,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -11813,7 +12589,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -11831,7 +12607,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -11849,7 +12625,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>

--- a/public/管理口径原因分析默认模版/上海物业项目部.xlsx
+++ b/public/管理口径原因分析默认模版/上海物业项目部.xlsx
@@ -9,20 +9,20 @@
   <sheets>
     <sheet sheetId="2" name="目录" state="visible" r:id="rId4"/>
     <sheet sheetId="3" name="合计" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="上海同盛大厦项目" state="visible" r:id="rId6"/>
-    <sheet sheetId="5" name="豪孚迪安保项目" state="visible" r:id="rId7"/>
-    <sheet sheetId="6" name="华东化工仓储安保项目" state="visible" r:id="rId8"/>
-    <sheet sheetId="7" name="寰球工程物业项目_合并" state="visible" r:id="rId9"/>
-    <sheet sheetId="8" name="寰球工程物业项目_222200150224" state="visible" r:id="rId10"/>
-    <sheet sheetId="9" name="寰球工程物业项目_222200150225" state="visible" r:id="rId11"/>
-    <sheet sheetId="10" name="长泰影院保洁项目" state="visible" r:id="rId12"/>
-    <sheet sheetId="11" name="川沙影院保洁项目" state="visible" r:id="rId13"/>
-    <sheet sheetId="12" name="上海世纪大道中石油综合物业项目" state="visible" r:id="rId14"/>
-    <sheet sheetId="13" name="上海世纪大道中石油综合餐饮项目" state="visible" r:id="rId15"/>
-    <sheet sheetId="14" name="世纪大道中石油上海大厦能源转售项目" state="visible" r:id="rId16"/>
-    <sheet sheetId="15" name="中石油上海临港新材料研究院配餐项目" state="visible" r:id="rId17"/>
-    <sheet sheetId="16" name="中石油上海临港新材料研究院物业项目" state="visible" r:id="rId18"/>
-    <sheet sheetId="17" name="陆家嘴金融城白领文化艺术中心物业项目" state="visible" r:id="rId19"/>
+    <sheet sheetId="4" name="同盛大厦租赁" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="豪孚迪安保" state="visible" r:id="rId7"/>
+    <sheet sheetId="6" name="华东化工安保" state="visible" r:id="rId8"/>
+    <sheet sheetId="7" name="寰球工程物业_合并" state="visible" r:id="rId9"/>
+    <sheet sheetId="8" name="寰球工程物业_222200150224" state="visible" r:id="rId10"/>
+    <sheet sheetId="9" name="寰球工程物业_222200150225" state="visible" r:id="rId11"/>
+    <sheet sheetId="10" name="长泰影院保洁" state="visible" r:id="rId12"/>
+    <sheet sheetId="11" name="川沙影院保洁" state="visible" r:id="rId13"/>
+    <sheet sheetId="12" name="世纪大道物业" state="visible" r:id="rId14"/>
+    <sheet sheetId="13" name="世纪大道餐饮" state="visible" r:id="rId15"/>
+    <sheet sheetId="14" name="世纪大道能源转售" state="visible" r:id="rId16"/>
+    <sheet sheetId="15" name="临港研究院配餐" state="visible" r:id="rId17"/>
+    <sheet sheetId="16" name="临港研究院物业" state="visible" r:id="rId18"/>
+    <sheet sheetId="17" name="陆家嘴白领艺术中心" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -46,46 +46,46 @@
     <t>合计</t>
   </si>
   <si>
-    <t>上海同盛大厦项目</t>
+    <t>同盛大厦租赁</t>
   </si>
   <si>
-    <t>豪孚迪安保项目</t>
+    <t>豪孚迪安保</t>
   </si>
   <si>
-    <t>华东化工仓储安保项目</t>
+    <t>华东化工安保</t>
   </si>
   <si>
-    <t>寰球工程物业项目_合并</t>
+    <t>寰球工程物业_合并</t>
   </si>
   <si>
-    <t>寰球工程物业项目_222200150224</t>
+    <t>寰球工程物业_222200150224</t>
   </si>
   <si>
-    <t>寰球工程物业项目_222200150225</t>
+    <t>寰球工程物业_222200150225</t>
   </si>
   <si>
-    <t>长泰影院保洁项目</t>
+    <t>长泰影院保洁</t>
   </si>
   <si>
-    <t>川沙影院保洁项目</t>
+    <t>川沙影院保洁</t>
   </si>
   <si>
-    <t>上海世纪大道中石油综合物业项目</t>
+    <t>世纪大道物业</t>
   </si>
   <si>
-    <t>上海世纪大道中石油综合餐饮项目</t>
+    <t>世纪大道餐饮</t>
   </si>
   <si>
-    <t>世纪大道中石油上海大厦能源转售项目</t>
+    <t>世纪大道能源转售</t>
   </si>
   <si>
-    <t>中石油上海临港新材料研究院配餐项目</t>
+    <t>临港研究院配餐</t>
   </si>
   <si>
-    <t>中石油上海临港新材料研究院物业项目</t>
+    <t>临港研究院物业</t>
   </si>
   <si>
-    <t>陆家嘴金融城白领文化艺术中心物业项目</t>
+    <t>陆家嘴白领艺术中心</t>
   </si>
   <si>
     <t>合计预算执行分析（2026年08月）</t>
@@ -289,7 +289,7 @@
     <t>四、净利润</t>
   </si>
   <si>
-    <t>上海同盛大厦项目预算执行分析（2026年08月）</t>
+    <t>同盛大厦租赁预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>出租率、平均单价同比均下降</t>
@@ -307,34 +307,34 @@
     <t>因出租率下降，中介费减少</t>
   </si>
   <si>
-    <t>豪孚迪安保项目预算执行分析（2026年08月）</t>
+    <t>豪孚迪安保预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>华东化工仓储安保项目预算执行分析（2026年08月）</t>
+    <t>华东化工安保预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>寰球工程物业项目_合并预算执行分析（2026年08月）</t>
+    <t>寰球工程物业_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>上年同期部分外包支出未入账</t>
   </si>
   <si>
-    <t>寰球工程物业项目_222200150224预算执行分析（2026年08月）</t>
+    <t>寰球工程物业_222200150224预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>寰球工程物业项目_222200150225预算执行分析（2026年08月）</t>
+    <t>寰球工程物业_222200150225预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>长泰影院保洁项目预算执行分析（2026年08月）</t>
+    <t>长泰影院保洁预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>此项目今年终止</t>
   </si>
   <si>
-    <t>川沙影院保洁项目预算执行分析（2026年08月）</t>
+    <t>川沙影院保洁预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>上海世纪大道中石油综合物业项目预算执行分析（2026年08月）</t>
+    <t>世纪大道物业预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>1、新增代售酒水收入167万元；2、增加礼仪人工收入302万元</t>
@@ -355,7 +355,7 @@
     <t>与预算周期不同</t>
   </si>
   <si>
-    <t>上海世纪大道中石油综合餐饮项目预算执行分析（2026年08月）</t>
+    <t>世纪大道餐饮预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>今年入账了上年80万收入，且上年同期约50万元当期收入未进账</t>
@@ -379,16 +379,16 @@
     <t>1、今年食材成本率相比预算下降约29%；2、商品销售收入增加86万元；3、压降用工成本等经营费用</t>
   </si>
   <si>
-    <t>世纪大道中石油上海大厦能源转售项目预算执行分析（2026年08月）</t>
+    <t>世纪大道能源转售预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>中石油上海临港新材料研究院配餐项目预算执行分析（2026年08月）</t>
+    <t>临港研究院配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>该项目为上年新增项目</t>
   </si>
   <si>
-    <t>中石油上海临港新材料研究院物业项目预算执行分析（2026年08月）</t>
+    <t>临港研究院物业预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>甲方今年严格控制成本费用发生</t>
@@ -403,7 +403,7 @@
     <t>上年同期对应收入未完全进账</t>
   </si>
   <si>
-    <t>陆家嘴金融城白领文化艺术中心物业项目预算执行分析（2026年08月）</t>
+    <t>陆家嘴白领艺术中心预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>上年同期部分收入未进账</t>
@@ -7119,7 +7119,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="5" t="str">
-        <f>HYPERLINK("#'上海同盛大厦项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'同盛大厦租赁'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="5" t="str">
-        <f>HYPERLINK("#'豪孚迪安保项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'豪孚迪安保'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="5" t="str">
-        <f>HYPERLINK("#'华东化工仓储安保项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'华东化工安保'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="5" t="str">
-        <f>HYPERLINK("#'寰球工程物业项目_合并'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'寰球工程物业_合并'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="5" t="str">
-        <f>HYPERLINK("#'寰球工程物业项目_222200150224'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'寰球工程物业_222200150224'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7169,7 +7169,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="5" t="str">
-        <f>HYPERLINK("#'寰球工程物业项目_222200150225'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'寰球工程物业_222200150225'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7179,7 +7179,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="5" t="str">
-        <f>HYPERLINK("#'长泰影院保洁项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'长泰影院保洁'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7189,7 +7189,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="5" t="str">
-        <f>HYPERLINK("#'川沙影院保洁项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'川沙影院保洁'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7199,7 +7199,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="5" t="str">
-        <f>HYPERLINK("#'上海世纪大道中石油综合物业项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'世纪大道物业'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="5" t="str">
-        <f>HYPERLINK("#'上海世纪大道中石油综合餐饮项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'世纪大道餐饮'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="5" t="str">
-        <f>HYPERLINK("#'世纪大道中石油上海大厦能源转售项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'世纪大道能源转售'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="5" t="str">
-        <f>HYPERLINK("#'中石油上海临港新材料研究院配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'临港研究院配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
         <v>17</v>
       </c>
       <c r="C16" s="5" t="str">
-        <f>HYPERLINK("#'中石油上海临港新材料研究院物业项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'临港研究院物业'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="5" t="str">
-        <f>HYPERLINK("#'陆家嘴金融城白领文化艺术中心物业项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'陆家嘴白领艺术中心'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
